--- a/artfynd/A 52007-2025 artfynd.xlsx
+++ b/artfynd/A 52007-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16895651</v>
+        <v>16895653</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödhusbergets SV-sida, 1400 m SO Lövhyddan, Jmt</t>
+          <t>Rödhusberget, 1500 m OSO Lövhyddan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462728.5317626088</v>
+        <v>462873</v>
       </c>
       <c r="R2" t="n">
-        <v>6924696.769189268</v>
+        <v>6924817</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -778,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3 substratenheter # gamla hårda tallågor</t>
+          <t>1 substratenheter # äldre tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,12 +792,7 @@
         <v>16895654</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463018.4432156892</v>
+        <v>463018</v>
       </c>
       <c r="R3" t="n">
-        <v>6925005.523369514</v>
+        <v>6925006</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +857,9 @@
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-05-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16895653</v>
+        <v>16895651</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,34 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rödhusberget, 1500 m OSO Lövhyddan, Jmt</t>
+          <t>Rödhusbergets SV-sida, 1400 m SO Lövhyddan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462873.1128198709</v>
+        <v>462729</v>
       </c>
       <c r="R4" t="n">
-        <v>6924816.897594646</v>
+        <v>6924697</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,21 +971,11 @@
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,11 +991,11 @@
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre tallåga</t>
+          <t>3 substratenheter # gamla hårda tallågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1062,50 +1017,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16895655</v>
+        <v>16895656</v>
       </c>
       <c r="B5" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödhusberget, 1600 m OSO Lövhyddan, Jmt</t>
+          <t>Rödhusberget, NO toppen, 1600 m OSO Lövhyddan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463018.4432156892</v>
+        <v>463114</v>
       </c>
       <c r="R5" t="n">
-        <v>6925005.523369514</v>
+        <v>6925163</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,21 +1085,11 @@
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-05-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1165,11 +1105,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # äldre tallåga</t>
+          <t>2 substratenheter # vitrötad splint på grova gamla torrakor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,6 +1124,120 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16895655</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rödhusberget, 1600 m OSO Lövhyddan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>463018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6925006</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-05-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-05-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>olikåldrig blåbärstallskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # äldre tallåga</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
